--- a/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -592,6 +592,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1" s="13">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -788,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="13" customHeight="1" s="13">
       <c r="A32" s="9" t="inlineStr">
         <is>
@@ -5158,7 +5160,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>함께 먹는 끼니 정하기</t>
+          <t>하루 한 끼는 여유 있게</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5172,7 +5174,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>함께 먹으면 천천히, 즐겁게 먹게 돼요.</t>
+          <t>끼니 하나를 정해 두면 천천히 즐겁게 먹게 돼요.</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
@@ -5191,7 +5193,11 @@
         </is>
       </c>
       <c r="M56" s="3" t="n"/>
-      <c r="N56" s="3" t="n"/>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O56" s="3" t="n"/>
       <c r="P56" s="11" t="inlineStr">
         <is>
@@ -5205,7 +5211,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>Plan a meal to share</t>
+          <t>One unhurried meal a day</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6400,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>면 요리에 채소 넣기</t>
+          <t>끓일 때 채소 한 줌 넣기</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -6429,7 +6435,7 @@
       <c r="M72" s="3" t="n"/>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O72" s="3" t="n"/>
@@ -6445,7 +6451,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>Add veggies to noodles</t>
+          <t>Add a handful of veggies</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9030,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>도시락에 단백질 담기</t>
+          <t>내일 단백질 반찬 담기</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -9038,7 +9044,7 @@
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>도시락에 담으면 밖에서도 단백질을 챙겨요.</t>
+          <t>미리 담아 두면 밖에서도 단백질을 챙겨요.</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr">
@@ -9057,7 +9063,11 @@
         </is>
       </c>
       <c r="M106" s="3" t="n"/>
-      <c r="N106" s="3" t="n"/>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O106" s="3" t="n"/>
       <c r="P106" s="11" t="inlineStr">
         <is>
@@ -9071,7 +9081,7 @@
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>Pack protein in your lunch</t>
+          <t>Pack protein for tomorrow</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10310,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>면 요리에 콩나물 한 줌</t>
+          <t>끓일 때 콩나물 한 줌</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
@@ -10314,7 +10324,7 @@
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>콩나물을 넣으면 면 요리에도 채소가 더해져요.</t>
+          <t>콩나물을 넣으면 한 그릇에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr">
@@ -10335,7 +10345,7 @@
       <c r="M122" s="3" t="n"/>
       <c r="N122" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O122" s="3" t="n"/>
@@ -10351,7 +10361,7 @@
       </c>
       <c r="R122" s="3" t="inlineStr">
         <is>
-          <t>Add sprouts to noodles</t>
+          <t>Add sprouts when cooking</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10553,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>면 요리에 달걀 하나</t>
+          <t>끓일 때 달걀 하나 넣기</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -10557,7 +10567,7 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>달걀을 넣으면 면 요리에도 단백질이 더해져요.</t>
+          <t>달걀을 넣으면 한 그릇에 단백질이 더해져요.</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr">
@@ -10578,7 +10588,7 @@
       <c r="M125" s="3" t="n"/>
       <c r="N125" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O125" s="3" t="n"/>
@@ -10594,7 +10604,7 @@
       </c>
       <c r="R125" s="3" t="inlineStr">
         <is>
-          <t>Add an egg to noodles</t>
+          <t>Add an egg when cooking</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11035,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>분말 스프는 반만</t>
+          <t>양념은 절반만 넣기</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -11039,7 +11049,7 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>스프를 반만 넣으면 나트륨이 크게 줄어요.</t>
+          <t>양념을 반만 넣으면 나트륨이 크게 줄어요.</t>
         </is>
       </c>
       <c r="J131" s="11" t="inlineStr">
@@ -11060,7 +11070,7 @@
       <c r="M131" s="3" t="n"/>
       <c r="N131" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O131" s="3" t="n"/>
@@ -11076,7 +11086,7 @@
       </c>
       <c r="R131" s="3" t="inlineStr">
         <is>
-          <t>Use half the soup powder</t>
+          <t>Half the seasoning</t>
         </is>
       </c>
     </row>

--- a/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -592,7 +592,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16" customHeight="1" s="13">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -789,7 +788,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="13" customHeight="1" s="13">
       <c r="A32" s="9" t="inlineStr">
         <is>
@@ -2213,7 +2211,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -2251,7 +2249,11 @@
         </is>
       </c>
       <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「A 대신 B」꼴은 기본 단계로</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="n"/>
       <c r="P18" s="11" t="inlineStr">
         <is>
@@ -2833,7 +2835,7 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -2871,7 +2873,11 @@
         </is>
       </c>
       <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「A 대신 B」꼴은 기본 단계로</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="n"/>
       <c r="P26" s="11" t="inlineStr">
         <is>
@@ -2910,7 +2916,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2948,7 +2954,11 @@
         </is>
       </c>
       <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「A 대신 B」꼴은 기본 단계로</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="n"/>
       <c r="P27" s="11" t="inlineStr">
         <is>
@@ -4929,7 +4939,7 @@
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>저녁은 매일 7시쯤</t>
+          <t>저녁은 매일 같은 시간에</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -4962,7 +4972,11 @@
         </is>
       </c>
       <c r="M53" s="3" t="n"/>
-      <c r="N53" s="3" t="n"/>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>10-19 특정 시각 전제 없이</t>
+        </is>
+      </c>
       <c r="O53" s="3" t="n"/>
       <c r="P53" s="11" t="inlineStr">
         <is>
@@ -4976,7 +4990,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>Dinner around 7 pm daily</t>
+          <t>Dinner at a set time daily</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9120,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -9146,7 +9160,7 @@
       <c r="M107" s="3" t="n"/>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O107" s="3" t="n"/>
@@ -9187,7 +9201,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
@@ -9227,7 +9241,7 @@
       <c r="M108" s="3" t="n"/>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O108" s="3" t="n"/>
@@ -9503,7 +9517,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
@@ -9543,7 +9557,7 @@
       <c r="M112" s="3" t="n"/>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O112" s="3" t="n"/>
@@ -9584,7 +9598,7 @@
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -9624,7 +9638,7 @@
       <c r="M113" s="3" t="n"/>
       <c r="N113" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O113" s="3" t="n"/>
@@ -9665,7 +9679,7 @@
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -9705,7 +9719,7 @@
       <c r="M114" s="3" t="n"/>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O114" s="3" t="n"/>
@@ -9746,7 +9760,7 @@
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -9786,7 +9800,7 @@
       <c r="M115" s="3" t="n"/>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O115" s="3" t="n"/>
@@ -9827,7 +9841,7 @@
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
@@ -9867,7 +9881,7 @@
       <c r="M116" s="3" t="n"/>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O116" s="3" t="n"/>
@@ -9908,7 +9922,7 @@
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -9948,7 +9962,7 @@
       <c r="M117" s="3" t="n"/>
       <c r="N117" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O117" s="3" t="n"/>
@@ -9989,7 +10003,7 @@
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -10029,7 +10043,7 @@
       <c r="M118" s="3" t="n"/>
       <c r="N118" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O118" s="3" t="n"/>
@@ -10787,7 +10801,7 @@
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
@@ -10827,7 +10841,7 @@
       <c r="M128" s="3" t="n"/>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O128" s="3" t="n"/>
@@ -11192,7 +11206,7 @@
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
@@ -11232,7 +11246,7 @@
       <c r="M133" s="3" t="n"/>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O133" s="3" t="n"/>
@@ -11273,7 +11287,7 @@
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
@@ -11313,7 +11327,7 @@
       <c r="M134" s="3" t="n"/>
       <c r="N134" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O134" s="3" t="n"/>
@@ -18875,7 +18889,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>

--- a/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -592,6 +592,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1" s="13">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -788,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="13" customHeight="1" s="13">
       <c r="A32" s="9" t="inlineStr">
         <is>
@@ -18889,6 +18891,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>

--- a/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>먹기 편한 시간 적기</t>
+          <t>먹기 편한 시간 적어보기</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2409,7 +2409,11 @@
         </is>
       </c>
       <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「적어보기」로</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="11" t="inlineStr">
         <is>
@@ -2423,7 +2427,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>Note when eating feels easy</t>
+          <t>Note your easy-eating times</t>
         </is>
       </c>
     </row>
